--- a/survey_templates/048_virtual_hardware_tutor_survey--survey_templates.xlsx
+++ b/survey_templates/048_virtual_hardware_tutor_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>satisfaction_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Satisfaction 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>technical_issues</t>
+          <t>technical_issues_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technical Issues</t>
+          <t>Technical Issues 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>learning_impact</t>
+          <t>learning_impact_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Learning Impact</t>
+          <t>Learning Impact 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -733,9 +733,9 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -882,148 +882,148 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>learning_impact_choices</t>
+          <t>learning_impact_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>learning_impact_choices</t>
+          <t>learning_impact_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>learning_impact_choices</t>
+          <t>learning_impact_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>learning_impact_choices</t>
+          <t>learning_impact_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
